--- a/TDD_examples/CASE_3_HTS_HVDC/conductor_1_coupling.xlsx
+++ b/TDD_examples/CASE_3_HTS_HVDC/conductor_1_coupling.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="contact_perimeter_flag" sheetId="8" r:id="R587fd9b963a74ef4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="contact_perimeter" sheetId="1" r:id="Rfdbe1eabc51e4681"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HTC_choice" sheetId="4" r:id="R80754895ec674f80"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="contact_HTC" sheetId="2" r:id="R08aecf4b6f3743ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="thermal_contact_resistance" sheetId="10" r:id="Re15b2c989fcf483c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HTC_multiplier" sheetId="5" r:id="R15a4f4430f4c44ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="electric_conductance_mode" sheetId="11" r:id="R46d2930ead004e5f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="electric_conductance" sheetId="12" r:id="Rbc76c079c7ad4cbe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="open_perimeter_fract" sheetId="3" r:id="Rc5ba8adc666947a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="interf_thickness" sheetId="7" r:id="Rb60d90dea9a24661"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="trans_transp_multiplier" sheetId="6" r:id="Ra51680fa3dae4c4d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="view_factors" sheetId="9" r:id="Rbb0a0cbe1fb14952"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="contact_perimeter_flag" sheetId="8" r:id="R8222f431c34f4fae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="contact_perimeter" sheetId="1" r:id="Re7d9d10f90ad4753"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HTC_choice" sheetId="4" r:id="Rc4fd2b5c6c7b4b83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="contact_HTC" sheetId="2" r:id="R924cc2e537a3472a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="thermal_contact_resistance" sheetId="10" r:id="Rd3098d72c1db4ad8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HTC_multiplier" sheetId="5" r:id="R6725c60f2ea84323"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="electric_conductance_mode" sheetId="11" r:id="R86320a18e9d348f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="electric_conductance" sheetId="12" r:id="Rec615147d0db4beb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="open_perimeter_fract" sheetId="3" r:id="Rdc6bac3282da4c46"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="interf_thickness" sheetId="7" r:id="R2c7d1bd826e540a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="trans_transp_multiplier" sheetId="6" r:id="R6ec2e66145344c2b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="view_factors" sheetId="9" r:id="R50236d6359fb4eaf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2843,7 +2843,7 @@
       <x:c r="A1" s="12"/>
       <x:c r="B1" s="12"/>
       <x:c r="C1" s="13" t="str">
-        <x:v>%[] flag to define the model to compute the HTC (yellow cells are those to thake into account). flag to decide how to evaluate interface htc.</x:v>
+        <x:v>%[] Flag used to select the HTC model (yellow cells are taken into account). This flag determines how the interface HTC is evaluated.</x:v>
       </x:c>
       <x:c r="D1" s="13"/>
       <x:c r="E1" s="13"/>
@@ -3690,7 +3690,7 @@
       <x:c r="A1" s="12"/>
       <x:c r="B1" s="12"/>
       <x:c r="C1" s="12" t="str">
-        <x:v>[m2K/W] thermal contact resistance between soldi component, should be &gt;= 0; used if flag HTC_choice is 1</x:v>
+        <x:v>[m2 K/W] Thermal contact resistance between solid components; it must be &gt;= 0. Used if HTC_choice is 1.</x:v>
       </x:c>
       <x:c r="D1" s="12"/>
       <x:c r="E1" s="12"/>
@@ -4537,7 +4537,7 @@
       <x:c r="A1" s="12"/>
       <x:c r="B1" s="12"/>
       <x:c r="C1" s="12" t="str">
-        <x:v>Flag to specify the kind of electric conductance: 1 conductance per unit length (the contact is along a line as for tow cilinder); 2 = actual conductance between components.</x:v>
+        <x:v>Flag used to specify the electric conductance: 1 = conductance per unit length (the contact is along a line, as for two cylinders); 2 = actual conductance between components.</x:v>
       </x:c>
       <x:c r="D1" s="12"/>
       <x:c r="E1" s="12"/>
